--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486521_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486521_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6119</v>
+        <v>6.6774</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4385</v>
+        <v>3.1032</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1735</v>
+        <v>3.5742</v>
       </c>
       <c r="G2" t="n">
         <v>3.8243</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2123</v>
+        <v>-0.1469</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7246</v>
+        <v>0.3894</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.5363</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9868</v>
+        <v>6.5571</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5293</v>
+        <v>3.9763</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4575</v>
+        <v>2.5808</v>
       </c>
       <c r="G3" t="n">
         <v>4.6508</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2519</v>
+        <v>0.3184</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1166</v>
+        <v>0.5636</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3685</v>
+        <v>-0.2452</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3698</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8644</v>
+        <v>5.2307</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8757</v>
+        <v>3.6494</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9887</v>
+        <v>1.5813</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5503</v>
+        <v>5.1499</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9295</v>
+        <v>2.8709</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6208</v>
+        <v>2.279</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9965</v>
+        <v>4.1301</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2698</v>
+        <v>2.4272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7267</v>
+        <v>1.7029</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5538</v>
+        <v>1.0198</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6597</v>
+        <v>0.4437</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8941</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5311</v>
+        <v>0.7333</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6187</v>
+        <v>0.6069</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0876</v>
+        <v>0.1265</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8695</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8434</v>
+        <v>4.7847</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9847</v>
+        <v>2.9798</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8587</v>
+        <v>1.8049</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1499</v>
+        <v>3.5074</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8709</v>
+        <v>3.0962</v>
       </c>
       <c r="I5" t="n">
-        <v>2.279</v>
+        <v>0.4112</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1301</v>
+        <v>2.8055</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4272</v>
+        <v>2.6525</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7029</v>
+        <v>0.153</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0198</v>
+        <v>0.7019</v>
       </c>
       <c r="N5" t="n">
         <v>0.4437</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.2582</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>1.9576</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>1.346</v>
+        <v>0.9941</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9421</v>
+        <v>0.9361</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4039</v>
+        <v>0.058</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.6743</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.6094</v>
+        <v>4.4694</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6504</v>
+        <v>3.7581</v>
       </c>
       <c r="F6" t="n">
-        <v>1.959</v>
+        <v>0.7113</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5074</v>
+        <v>5.5503</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0962</v>
+        <v>3.9295</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4112</v>
+        <v>1.6208</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8055</v>
+        <v>3.9965</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6525</v>
+        <v>3.2698</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153</v>
+        <v>0.7267</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7019</v>
+        <v>1.5538</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4437</v>
+        <v>0.6597</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2582</v>
+        <v>0.8941</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8188</v>
+        <v>0.1361</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6067</v>
+        <v>0.5011</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2121</v>
+        <v>-0.365</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6743</v>
+        <v>-1.8695</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.5443</v>
+        <v>-0.7395</v>
       </c>
       <c r="X6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.192</v>
+        <v>3.9126</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7724</v>
+        <v>2.5547</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4196</v>
+        <v>1.3579</v>
       </c>
       <c r="G7" t="n">
         <v>2.2437</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6167</v>
+        <v>0.1039</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4795</v>
+        <v>0.3028</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1372</v>
+        <v>-0.1989</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6267</v>
+        <v>3.0044</v>
       </c>
       <c r="E8" t="n">
-        <v>2.319</v>
+        <v>2.5425</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3078</v>
+        <v>0.4619</v>
       </c>
       <c r="G8" t="n">
         <v>2.6818</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6423</v>
+        <v>-0.2647</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0324</v>
+        <v>0.1911</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6099</v>
+        <v>-0.4558</v>
       </c>
       <c r="V8" t="n">
         <v>0.3698</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3084</v>
+        <v>0.8363</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7335</v>
+        <v>1.2923</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4251</v>
+        <v>-0.456</v>
       </c>
       <c r="G10" t="n">
         <v>1.9762</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9951</v>
+        <v>-0.4672</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.0577</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3787</v>
+        <v>-0.4095</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0378</v>
+        <v>0.3962</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.923</v>
+        <v>-1.8113</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9608</v>
+        <v>2.2074</v>
       </c>
       <c r="G11" t="n">
         <v>0.8804</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2449</v>
+        <v>0.6032</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4146</v>
+        <v>0.5264</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1697</v>
+        <v>0.0769</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0345</v>
+        <v>0.154</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6088</v>
+        <v>-1.2735</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6433</v>
+        <v>1.4276</v>
       </c>
       <c r="G12" t="n">
         <v>2.2461</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3561</v>
+        <v>0.4756</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.113</v>
+        <v>0.2223</v>
       </c>
       <c r="U12" t="n">
-        <v>0.469</v>
+        <v>0.2532</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5398</v>
+        <v>-1.4473</v>
       </c>
       <c r="E13" t="n">
         <v>-1.6235</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0837</v>
+        <v>0.1762</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4573</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0379</v>
+        <v>-0.9454</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.889</v>
       </c>
       <c r="V13" t="n">
         <v>0.3904</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>35.7116</v>
+        <v>35.71160000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>19.2652</v>
+        <v>19.265</v>
       </c>
       <c r="F14" t="n">
         <v>16.4465</v>
@@ -1537,7 +1537,7 @@
         <v>5.7612</v>
       </c>
       <c r="P14" t="n">
-        <v>2.175099999999999</v>
+        <v>2.1751</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.9627</v>
@@ -1546,19 +1546,19 @@
         <v>14.1378</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4722</v>
+        <v>1.4719</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2059</v>
+        <v>4.206</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.734</v>
+        <v>-2.7341</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5235999999999996</v>
       </c>
       <c r="W14" t="n">
-        <v>5.712</v>
+        <v>5.711999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-6.235599999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1639</v>
+        <v>1.5492</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6236</v>
+        <v>2.9473</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4598</v>
+        <v>-1.3981</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7819</v>
@@ -1624,13 +1624,13 @@
         <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3808</v>
+        <v>0.7661</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7423</v>
+        <v>1.0659</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3615</v>
+        <v>-0.2998</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4407</v>
+        <v>0.587</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4127</v>
+        <v>0.5657</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.972</v>
+        <v>0.0213</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1232</v>
+        <v>-2.4411</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2755</v>
+        <v>-1.6236</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1523</v>
+        <v>-0.8176</v>
       </c>
       <c r="J16" t="n">
-        <v>1.772</v>
+        <v>-0.9588</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2497</v>
+        <v>-0.6927</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0217</v>
+        <v>-0.2661</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8952</v>
+        <v>-1.4823</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0258</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8694</v>
+        <v>-0.5514</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1289</v>
+        <v>0.5507</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5983</v>
+        <v>0.3521</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4694</v>
+        <v>0.1986</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.176</v>
+        <v>0.2287</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1049</v>
+        <v>2.6304</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0712</v>
+        <v>-2.4017</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4411</v>
+        <v>-1.1232</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6236</v>
+        <v>-3.2755</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8176</v>
+        <v>2.1523</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9588</v>
+        <v>1.772</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6927</v>
+        <v>-1.2497</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2661</v>
+        <v>3.0217</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4823</v>
+        <v>-2.8952</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-2.0258</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5514</v>
+        <v>-0.8694</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2123</v>
+        <v>0.9169</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3184</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1061</v>
+        <v>0.1009</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2293</v>
+        <v>-0.8053</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.076</v>
+        <v>0.5945</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1532</v>
+        <v>-1.3998</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5666</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1199</v>
+        <v>0.304</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2379</v>
+        <v>0.4326</v>
       </c>
       <c r="U18" t="n">
-        <v>0.118</v>
+        <v>-0.1286</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4913</v>
+        <v>-1.4578</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7753</v>
+        <v>-2.5518</v>
       </c>
       <c r="F19" t="n">
-        <v>1.284</v>
+        <v>1.094</v>
       </c>
       <c r="G19" t="n">
         <v>0.1378</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1936</v>
+        <v>-0.1601</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3544</v>
+        <v>0.1643</v>
       </c>
       <c r="V19" t="n">
         <v>0.7395</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4356</v>
+        <v>-2.5121</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0397</v>
+        <v>-1.4809</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.396</v>
+        <v>-1.0312</v>
       </c>
       <c r="G20" t="n">
         <v>-2.653</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6527</v>
+        <v>-0.7291</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8992</v>
+        <v>-0.5345</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.885</v>
+        <v>-3.2298</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0452</v>
+        <v>-2.3746</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8399</v>
+        <v>-0.8552</v>
       </c>
       <c r="G21" t="n">
         <v>-2.097</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2878</v>
+        <v>0.3674</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6044</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3166</v>
+        <v>0.3013</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0363</v>
+        <v>-4.166</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2431</v>
+        <v>-0.0922</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.2794</v>
+        <v>-4.0738</v>
       </c>
       <c r="G22" t="n">
         <v>-1.482</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4659</v>
+        <v>0.3362</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0347</v>
+        <v>0.6994</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5688</v>
+        <v>-0.3632</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0202</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4238</v>
+        <v>-5.8856</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.863</v>
+        <v>-4.1983</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5608</v>
+        <v>-1.6873</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9496</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6695</v>
+        <v>-0.1313</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3377</v>
+        <v>0.0024</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0071</v>
+        <v>-0.1337</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3698</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.916399999999999</v>
+        <v>-8.2407</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5745</v>
+        <v>-5.351</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3419</v>
+        <v>-2.8898</v>
       </c>
       <c r="G24" t="n">
         <v>-7.1522</v>
@@ -2326,13 +2326,13 @@
         <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7637</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3148</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4488</v>
+        <v>0.0033</v>
       </c>
       <c r="V24" t="n">
         <v>0.7395</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.7224</v>
+        <v>-8.7988</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.2474</v>
+        <v>-7.1357</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.475</v>
+        <v>-1.6632</v>
       </c>
       <c r="G25" t="n">
         <v>-8.4793</v>
@@ -2404,13 +2404,13 @@
         <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5481</v>
+        <v>-0.6246</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2019</v>
+        <v>-0.0901</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3463</v>
+        <v>-0.5345</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5649999999999999</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-35.7115</v>
+        <v>-32.7312</v>
       </c>
       <c r="E26" t="n">
         <v>-16.4466</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.2652</v>
+        <v>-16.2848</v>
       </c>
       <c r="G26" t="n">
         <v>-32.5881</v>
@@ -2461,7 +2461,7 @@
         <v>-5.5171</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.7611</v>
+        <v>-5.761099999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-21.3099</v>
@@ -2482,13 +2482,13 @@
         <v>11.9626</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.472</v>
+        <v>1.5082</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7341</v>
+        <v>2.7339</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.206</v>
+        <v>-1.2259</v>
       </c>
       <c r="V26" t="n">
         <v>0.5235000000000003</v>
